--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484361_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484361_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1774</v>
+        <v>6.4734</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9054</v>
+        <v>3.2287</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2719</v>
+        <v>3.2447</v>
       </c>
       <c r="G2" t="n">
         <v>3.9651</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7081</v>
+        <v>1.0042</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4758</v>
+        <v>-0.1526</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1839</v>
+        <v>1.1567</v>
       </c>
       <c r="V2" t="n">
         <v>0.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5732</v>
+        <v>6.0744</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6652</v>
+        <v>3.7148</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0919</v>
+        <v>2.3596</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1029</v>
+        <v>5.3329</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1187</v>
+        <v>4.5915</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9842</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0211</v>
+        <v>4.6742</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0916</v>
+        <v>3.932</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9295</v>
+        <v>0.7422</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9182</v>
+        <v>0.6587</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9729</v>
+        <v>0.6595</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9453</v>
+        <v>-0.0008</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9662</v>
+        <v>0.6596</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6208</v>
+        <v>-0.3417</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3454</v>
+        <v>1.0013</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2772</v>
+        <v>0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0241</v>
+        <v>5.4141</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2093</v>
+        <v>4.4341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8149</v>
+        <v>0.98</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3329</v>
+        <v>3.8425</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5915</v>
+        <v>0.6861</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7413999999999999</v>
+        <v>3.1563</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6742</v>
+        <v>3.5874</v>
       </c>
       <c r="K4" t="n">
-        <v>3.932</v>
+        <v>1.1051</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7422</v>
+        <v>2.4822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6587</v>
+        <v>0.2551</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6595</v>
+        <v>-0.419</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0008</v>
+        <v>0.6741</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3907</v>
+        <v>0.099</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0399</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4566</v>
+        <v>0.1389</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5545</v>
+        <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9667</v>
+        <v>4.5487</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2318</v>
+        <v>4.6134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7349</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8425</v>
+        <v>3.1029</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6861</v>
+        <v>2.1187</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1563</v>
+        <v>0.9842</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5874</v>
+        <v>5.0211</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1051</v>
+        <v>3.0916</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4822</v>
+        <v>1.9295</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2551</v>
+        <v>-1.9182</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.419</v>
+        <v>-0.9729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6741</v>
+        <v>-0.9453</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3483</v>
+        <v>0.9417</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2421</v>
+        <v>0.569</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1062</v>
+        <v>0.3726</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8865</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7012</v>
+        <v>2.221</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8337</v>
+        <v>1.4898</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.7313</v>
       </c>
       <c r="G6" t="n">
         <v>0.1946</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2023</v>
+        <v>0.7222</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3936</v>
+        <v>0.0497</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8087</v>
+        <v>0.6725</v>
       </c>
       <c r="V6" t="n">
         <v>1.1089</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8044</v>
+        <v>1.6569</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4759</v>
+        <v>-1.0515</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2803</v>
+        <v>2.7084</v>
       </c>
       <c r="G7" t="n">
         <v>0.8136</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9089</v>
+        <v>0.7613</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.3019</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6352</v>
+        <v>1.0632</v>
       </c>
       <c r="V7" t="n">
         <v>0.2772</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4951</v>
+        <v>0.1083</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3278</v>
+        <v>-0.4695</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8229</v>
+        <v>0.5778</v>
       </c>
       <c r="G8" t="n">
         <v>0.2878</v>
@@ -1078,13 +1078,13 @@
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4928</v>
+        <v>1.106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4541</v>
+        <v>0.3124</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0387</v>
+        <v>0.7936</v>
       </c>
       <c r="V8" t="n">
         <v>0.2772</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7724</v>
+        <v>-0.4491</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4838</v>
+        <v>-1.1606</v>
       </c>
       <c r="F9" t="n">
         <v>0.7115</v>
@@ -1156,10 +1156,10 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4182</v>
+        <v>-0.095</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.652</v>
+        <v>-0.3287</v>
       </c>
       <c r="U9" t="n">
         <v>0.2337</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9702</v>
+        <v>-2.4429</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5409</v>
+        <v>-1.1771</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4292</v>
+        <v>-1.2658</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6203</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0493</v>
+        <v>-0.5221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3494</v>
+        <v>0.0145</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7</v>
+        <v>-0.5366</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>22.9995</v>
+        <v>23.6048</v>
       </c>
       <c r="E11" t="n">
-        <v>13.017</v>
+        <v>13.6221</v>
       </c>
       <c r="F11" t="n">
-        <v>9.982699999999999</v>
+        <v>9.982799999999999</v>
       </c>
       <c r="G11" t="n">
         <v>16.3231</v>
@@ -1282,7 +1282,7 @@
         <v>17.6722</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3492</v>
+        <v>-1.349200000000001</v>
       </c>
       <c r="J11" t="n">
         <v>20.8714</v>
@@ -1294,10 +1294,10 @@
         <v>4.0525</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.5484</v>
+        <v>-4.548400000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8534</v>
+        <v>0.8534000000000003</v>
       </c>
       <c r="O11" t="n">
         <v>-5.4017</v>
@@ -1312,13 +1312,13 @@
         <v>10.7438</v>
       </c>
       <c r="S11" t="n">
-        <v>4.071800000000001</v>
+        <v>4.6769</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8244</v>
+        <v>-0.2192000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>4.896</v>
+        <v>4.8959</v>
       </c>
       <c r="V11" t="n">
         <v>2.6047</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9636</v>
+        <v>3.2968</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6203</v>
+        <v>2.5192</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3432</v>
+        <v>0.7776</v>
       </c>
       <c r="G12" t="n">
         <v>4.8499</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6008</v>
+        <v>-0.2676</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4153</v>
+        <v>-0.5164</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1855</v>
+        <v>0.2489</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6303</v>
+        <v>1.2241</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0296</v>
+        <v>2.4341</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3993</v>
+        <v>-1.21</v>
       </c>
       <c r="G13" t="n">
         <v>2.4571</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2843</v>
+        <v>-0.6906</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.271</v>
+        <v>-0.8665</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0134</v>
+        <v>0.1759</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1052</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5763</v>
+        <v>-0.6479</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8388</v>
+        <v>-2.4909</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2625</v>
+        <v>1.843</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6494</v>
+        <v>-1.5654</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8123</v>
+        <v>-2.6856</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8371</v>
+        <v>1.1202</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1755</v>
+        <v>-1.0713</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9327</v>
+        <v>-1.6526</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2428</v>
+        <v>0.5813</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.8249</v>
+        <v>-0.4941</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.7449</v>
+        <v>-1.033</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0799</v>
+        <v>0.5389</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8704</v>
+        <v>0.3315</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0623</v>
+        <v>-0.4429</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8081</v>
+        <v>0.7744</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>E. PARADINAS DELGADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8331</v>
+        <v>-1.0623</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.8954</v>
+        <v>-0.1808</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0622</v>
+        <v>-0.8815</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5654</v>
+        <v>-1.8609</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.6856</v>
+        <v>-0.1481</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1202</v>
+        <v>-1.7128</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0713</v>
+        <v>-0.5722</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6526</v>
+        <v>0.0614</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5813</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4941</v>
+        <v>-1.2887</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.033</v>
+        <v>-0.2095</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5389</v>
+        <v>-1.0792</v>
       </c>
       <c r="P15" t="n">
         <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1463</v>
+        <v>0.2126</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.3914</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9936</v>
+        <v>-0.1789</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. PARADINAS DELGADO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0157</v>
+        <v>-1.1014</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.6254</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-1.7268</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8609</v>
+        <v>-1.6494</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1481</v>
+        <v>-0.8123</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7128</v>
+        <v>-0.8371</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5722</v>
+        <v>2.1755</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0614</v>
+        <v>1.9327</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.2428</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2887</v>
+        <v>-3.8249</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2095</v>
+        <v>-2.7449</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0792</v>
+        <v>-1.0799</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2592</v>
+        <v>0.1926</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4925</v>
+        <v>-0.1511</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2333</v>
+        <v>0.3437</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0882</v>
+        <v>-1.8237</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8107</v>
+        <v>-1.7096</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2775</v>
+        <v>-0.1141</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2947</v>
@@ -1780,13 +1780,13 @@
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4028</v>
+        <v>-0.1383</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0397</v>
+        <v>0.1238</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7544</v>
+        <v>-3.5716</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0366</v>
+        <v>-1.9355</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7178</v>
+        <v>-1.6361</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1156</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6388</v>
+        <v>-0.456</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4237</v>
+        <v>-0.3225</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1591</v>
+        <v>-4.381</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0025</v>
+        <v>-2.1249</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1566</v>
+        <v>-2.2561</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0954</v>
+        <v>-2.8128</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1911</v>
+        <v>-2.4354</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9043</v>
+        <v>-0.3774</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9342</v>
+        <v>0.9372</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7585</v>
+        <v>-0.3044</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1757</v>
+        <v>1.2416</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.0295</v>
+        <v>-3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.9496</v>
+        <v>-2.131</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0799</v>
+        <v>-1.619</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5679</v>
+        <v>-0.9821</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.96</v>
+        <v>-1.1086</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3921</v>
+        <v>0.1265</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0033</v>
+        <v>-4.5053</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5293</v>
+        <v>-1.1037</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.474</v>
+        <v>-3.4017</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8128</v>
+        <v>-3.0954</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4354</v>
+        <v>-2.1911</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3774</v>
+        <v>-0.9043</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9372</v>
+        <v>0.9342</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3044</v>
+        <v>0.7585</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2416</v>
+        <v>0.1757</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.75</v>
+        <v>-4.0295</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.131</v>
+        <v>-2.9496</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.619</v>
+        <v>-1.0799</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6045</v>
+        <v>-0.9141</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5131</v>
+        <v>-1.0611</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0914</v>
+        <v>0.147</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.3159</v>
+        <v>-9.7531</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.1171</v>
+        <v>-6.016</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.1988</v>
+        <v>-3.7371</v>
       </c>
       <c r="G21" t="n">
         <v>-8.2357</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2484</v>
+        <v>-0.6857</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6574</v>
+        <v>-0.5563</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.591</v>
+        <v>-0.1294</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8317</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.9995</v>
+        <v>-22.3254</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.9826</v>
+        <v>-9.982699999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.0171</v>
+        <v>-12.3428</v>
       </c>
       <c r="G22" t="n">
         <v>-16.3229</v>
@@ -2140,7 +2140,7 @@
         <v>-17.6722</v>
       </c>
       <c r="I22" t="n">
-        <v>1.349199999999998</v>
+        <v>1.3492</v>
       </c>
       <c r="J22" t="n">
         <v>4.548500000000002</v>
@@ -2158,10 +2158,10 @@
         <v>-16.8188</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.0525</v>
+        <v>-4.052499999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q22" t="n">
         <v>-10.7437</v>
@@ -2170,13 +2170,13 @@
         <v>10.7437</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.0716</v>
+        <v>-3.397699999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.8961</v>
+        <v>-4.896</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8243</v>
+        <v>1.4984</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6048</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484361_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484361_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.221</v>
+        <v>3.6629</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4898</v>
+        <v>3.6629</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7313</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1946</v>
+        <v>3.6629</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4758</v>
+        <v>1.8419</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2813</v>
+        <v>1.821</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5032</v>
+        <v>3.6629</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1092</v>
+        <v>1.8419</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.606</v>
+        <v>1.821</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3087</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7222</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0497</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6725</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6569</v>
+        <v>2.221</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0515</v>
+        <v>1.4898</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7084</v>
+        <v>0.7313</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8136</v>
+        <v>0.1946</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8944</v>
+        <v>1.4758</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-1.2813</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1452</v>
+        <v>1.5032</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.449</v>
+        <v>2.1092</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5942</v>
+        <v>-0.606</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6685</v>
+        <v>-1.3087</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3433</v>
+        <v>-0.6334</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.6753</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7613</v>
+        <v>0.7222</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3019</v>
+        <v>0.0497</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0632</v>
+        <v>0.6725</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>1.1089</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>1.1089</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1083</v>
+        <v>1.6569</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4695</v>
+        <v>-1.0515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5778</v>
+        <v>2.7084</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2878</v>
+        <v>0.8136</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9059</v>
+        <v>0.8944</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.618</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.871</v>
+        <v>0.1452</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2182</v>
+        <v>-0.449</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3472</v>
+        <v>0.5942</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5832</v>
+        <v>0.6685</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3123</v>
+        <v>1.3433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2708</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>1.106</v>
+        <v>0.7613</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3124</v>
+        <v>-0.3019</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7936</v>
+        <v>1.0632</v>
       </c>
       <c r="V8" t="n">
         <v>0.2772</v>
@@ -1094,6 +1129,11 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>23.6048</v>
+        <v>-3.5546</v>
       </c>
       <c r="E11" t="n">
-        <v>13.6221</v>
+        <v>-4.1324</v>
       </c>
       <c r="F11" t="n">
-        <v>9.982799999999999</v>
+        <v>0.5778</v>
       </c>
       <c r="G11" t="n">
-        <v>16.3231</v>
+        <v>-3.3751</v>
       </c>
       <c r="H11" t="n">
-        <v>17.6722</v>
+        <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.349200000000001</v>
+        <v>-3.439</v>
       </c>
       <c r="J11" t="n">
-        <v>20.8714</v>
+        <v>-1.7919</v>
       </c>
       <c r="K11" t="n">
-        <v>16.8188</v>
+        <v>1.3763</v>
       </c>
       <c r="L11" t="n">
-        <v>4.0525</v>
+        <v>-3.1682</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.548400000000001</v>
+        <v>-1.5832</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8534000000000003</v>
+        <v>-1.3123</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.4017</v>
+        <v>-0.2708</v>
       </c>
       <c r="P11" t="n">
-        <v>9.999999999965592e-05</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.7439</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7438</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6769</v>
+        <v>1.106</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2192000000000001</v>
+        <v>0.3124</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8959</v>
+        <v>0.7936</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6047</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7136</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2968</v>
+        <v>23.6048</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5192</v>
+        <v>13.6221</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7776</v>
+        <v>9.982799999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8499</v>
+        <v>16.3231</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3564</v>
+        <v>17.6721</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2063</v>
+        <v>-1.349200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>5.6885</v>
+        <v>20.8714</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2906</v>
+        <v>16.8188</v>
       </c>
       <c r="L12" t="n">
-        <v>4.3979</v>
+        <v>4.0525</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8386</v>
+        <v>-4.5484</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.647</v>
+        <v>0.8534000000000006</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8083</v>
+        <v>-5.4017</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5627</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-10.7439</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>10.7438</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2676</v>
+        <v>4.6769</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5164</v>
+        <v>-0.2192000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2489</v>
+        <v>4.895899999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>2.6047</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>3.7136</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.1088</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2241</v>
+        <v>3.2968</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4341</v>
+        <v>2.5192</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.21</v>
+        <v>0.7776</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4571</v>
+        <v>4.8499</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5086</v>
+        <v>-0.3564</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9656</v>
+        <v>5.2063</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3006</v>
+        <v>5.6885</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1433</v>
+        <v>1.2906</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1573</v>
+        <v>4.3979</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8435</v>
+        <v>-0.8386</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6518</v>
+        <v>-1.647</v>
       </c>
       <c r="O13" t="n">
         <v>0.8083</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6906</v>
+        <v>-0.2676</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8665</v>
+        <v>-0.5164</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1759</v>
+        <v>0.2489</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1052</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6479</v>
+        <v>1.2241</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4909</v>
+        <v>2.4341</v>
       </c>
       <c r="F14" t="n">
-        <v>1.843</v>
+        <v>-1.21</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5654</v>
+        <v>2.4571</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6856</v>
+        <v>-1.5086</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1202</v>
+        <v>3.9656</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0713</v>
+        <v>3.3006</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6526</v>
+        <v>0.1433</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5813</v>
+        <v>3.1573</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4941</v>
+        <v>-0.8435</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.033</v>
+        <v>-1.6518</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5389</v>
+        <v>0.8083</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3315</v>
+        <v>-0.6906</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4429</v>
+        <v>-0.8665</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7744</v>
+        <v>0.1759</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. PARADINAS DELGADO</t>
+          <t>À. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0623</v>
+        <v>0.307</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1808</v>
+        <v>0.307</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8815</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8609</v>
+        <v>0.307</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1481</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7128</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5722</v>
+        <v>0.307</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0614</v>
+        <v>0.307</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2887</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2095</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0792</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2126</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3914</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1789</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,12 +1706,17 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1014</v>
+        <v>-0.6479</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6254</v>
+        <v>-2.4909</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7268</v>
+        <v>1.843</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6494</v>
+        <v>-1.5654</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8123</v>
+        <v>-2.6856</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8371</v>
+        <v>1.1202</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1755</v>
+        <v>-1.0713</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9327</v>
+        <v>-1.6526</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2428</v>
+        <v>0.5813</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8249</v>
+        <v>-0.4941</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7449</v>
+        <v>-1.033</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0799</v>
+        <v>0.5389</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1926</v>
+        <v>0.3315</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1511</v>
+        <v>-0.4429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3437</v>
+        <v>0.7744</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ARNELLA I MAS</t>
+          <t>E. PARADINAS DELGADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8237</v>
+        <v>-1.0623</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7096</v>
+        <v>-0.1808</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1141</v>
+        <v>-0.8815</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2947</v>
+        <v>-1.8609</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7416</v>
+        <v>-0.1481</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5531</v>
+        <v>-1.7128</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4708</v>
+        <v>-0.5722</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0819</v>
+        <v>0.0614</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5527</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8239</v>
+        <v>-1.2887</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8235</v>
+        <v>-0.2095</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0004</v>
+        <v>-1.0792</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1383</v>
+        <v>0.2126</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.262</v>
+        <v>0.3914</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1238</v>
+        <v>-0.1789</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.5716</v>
+        <v>-1.1014</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9355</v>
+        <v>0.6254</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6361</v>
+        <v>-1.7268</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1156</v>
+        <v>-1.6494</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6324</v>
+        <v>-0.8123</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4832</v>
+        <v>-0.8371</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.613</v>
+        <v>2.1755</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2648</v>
+        <v>1.9327</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3482</v>
+        <v>0.2428</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5026</v>
+        <v>-3.8249</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3676</v>
+        <v>-2.7449</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>-1.0799</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.456</v>
+        <v>0.1926</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3225</v>
+        <v>-0.1511</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1335</v>
+        <v>0.3437</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>R. ARNELLA I MAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.381</v>
+        <v>-1.8237</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1249</v>
+        <v>-1.7096</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2561</v>
+        <v>-0.1141</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8128</v>
+        <v>-1.2947</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4354</v>
+        <v>-0.7416</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3774</v>
+        <v>-0.5531</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9372</v>
+        <v>-0.4708</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3044</v>
+        <v>0.0819</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2416</v>
+        <v>-0.5527</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.75</v>
+        <v>-0.8239</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.131</v>
+        <v>-0.8235</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.619</v>
+        <v>-0.0004</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9821</v>
+        <v>-0.1383</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1086</v>
+        <v>-0.262</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1265</v>
+        <v>0.1238</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5053</v>
+        <v>-3.8786</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1037</v>
+        <v>-2.2425</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4017</v>
+        <v>-1.6361</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0954</v>
+        <v>-3.4226</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1911</v>
+        <v>-1.9394</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9043</v>
+        <v>-1.4832</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9342</v>
+        <v>-1.92</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7585</v>
+        <v>-0.5718</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1757</v>
+        <v>-1.3482</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0295</v>
+        <v>-1.5026</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.9496</v>
+        <v>-1.3676</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0799</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9141</v>
+        <v>-0.456</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0611</v>
+        <v>-0.3225</v>
       </c>
       <c r="U20" t="n">
-        <v>0.147</v>
+        <v>-0.1335</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.7531</v>
+        <v>-4.381</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.016</v>
+        <v>-2.1249</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7371</v>
+        <v>-2.2561</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.2357</v>
+        <v>-2.8128</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.1607</v>
+        <v>-2.4354</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.075</v>
+        <v>-0.3774</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.7602</v>
+        <v>0.9372</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.8998</v>
+        <v>-0.3044</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8604</v>
+        <v>1.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4755</v>
+        <v>-3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2609</v>
+        <v>-2.131</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2146</v>
+        <v>-1.619</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6857</v>
+        <v>-0.9821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5563</v>
+        <v>-1.1086</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1294</v>
+        <v>0.1265</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1089</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,235 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-4.5053</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.1037</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.4017</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.0954</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.1911</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.9043</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-4.0295</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-2.9496</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.0799</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.9141</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.0611</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M. CAPELL OLLER</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-9.7531</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-6.016</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.7371</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-8.2357</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-5.1607</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-3.075</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-4.7602</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2.8998</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.8604</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-3.4755</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.2609</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.6857</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5563</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.1294</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.1089</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484361_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-22.3254</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>-9.982699999999999</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>-12.3428</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G24" t="n">
         <v>-16.3229</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H24" t="n">
         <v>-17.6722</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>1.3492</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>4.548500000000002</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>-0.8532000000000002</v>
       </c>
-      <c r="L22" t="n">
-        <v>5.4017</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L24" t="n">
+        <v>5.401699999999999</v>
+      </c>
+      <c r="M24" t="n">
         <v>-20.8713</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N24" t="n">
         <v>-16.8188</v>
       </c>
-      <c r="O22" t="n">
-        <v>-4.052499999999999</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-5.551115123125783e-17</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="O24" t="n">
+        <v>-4.0525</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-10.7437</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>10.7437</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>-3.397699999999999</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>-4.896</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>1.4984</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V24" t="n">
         <v>-2.6048</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W24" t="n">
         <v>1.1089</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X24" t="n">
         <v>-3.7137</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
